--- a/data/trans_orig/IP16A98-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A98-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>12445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>10522</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16482</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>24607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31794</t>
+          <t>32001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>16972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22165</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18088</t>
+          <t>17954</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23119</t>
+          <t>23110</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37337</t>
+          <t>37219</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44010</t>
+          <t>44143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>691</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>16386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20962</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28398</t>
+          <t>28425</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14529</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26152</t>
+          <t>26163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32105</t>
+          <t>32520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>11007</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21282</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10193</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12113</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17408</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>26823</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>10834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20911</t>
+          <t>21217</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>17426</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>23504</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40965</t>
+          <t>41070</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49175</t>
+          <t>49201</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>15137</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>18673</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11363</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18433</t>
+          <t>18544</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26323</t>
+          <t>26391</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35738</t>
+          <t>35438</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24369</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31573</t>
+          <t>31501</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32332</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51700</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>119744</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>132893</t>
+          <t>132808</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>122982</t>
+          <t>123054</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>138009</t>
+          <t>138067</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>247444</t>
+          <t>247471</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>266839</t>
+          <t>267594</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14898</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18643</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24914</t>
+          <t>25814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32661</t>
+          <t>32590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9269</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26601</t>
+          <t>26606</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38676</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45689</t>
+          <t>45909</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -4741,62 +4741,62 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5187</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>54,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5142</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,58%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4257</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>17,42%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4232</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,49 +4869,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>92,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6887</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4082</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8339</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>82,58%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>48,95%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6887</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4107</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>8339</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>82,58%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>49,25%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>20</t>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16381</t>
+          <t>16386</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>12620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20441</t>
+          <t>20426</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20425</t>
+          <t>20146</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>20985</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28938</t>
+          <t>28953</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39933</t>
+          <t>39460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15510</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,38%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>529</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9612</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13676</t>
+          <t>13721</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>24246</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20261</t>
+          <t>20312</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15377</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21874</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33225</t>
+          <t>33062</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41013</t>
+          <t>40808</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29345</t>
+          <t>29441</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33834</t>
+          <t>33523</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37240</t>
+          <t>37927</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56783</t>
+          <t>58056</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>98116</t>
+          <t>98020</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>111758</t>
+          <t>112221</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>89753</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>104959</t>
+          <t>104254</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>193954</t>
+          <t>192681</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>213497</t>
+          <t>212810</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19602</t>
+          <t>20566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27772</t>
+          <t>27917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>15011</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46586</t>
+          <t>46713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19679</t>
+          <t>19690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47142</t>
+          <t>47121</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61633</t>
+          <t>61888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38836</t>
+          <t>39136</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46302</t>
+          <t>46082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91538</t>
+          <t>91527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106235</t>
+          <t>105904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16799</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17973</t>
+          <t>17866</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23770</t>
+          <t>25005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33389</t>
+          <t>33544</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11490</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>14543</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12621</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14895</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20046</t>
+          <t>20028</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25832</t>
+          <t>26201</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20873</t>
+          <t>20940</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27783</t>
+          <t>27720</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24257</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40260</t>
+          <t>39885</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>48308</t>
+          <t>47939</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>65781</t>
+          <t>65888</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>9920</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>50,05%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>16859</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>49092</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>23963</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>46435</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>46865</t>
+          <t>49549</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>85107</t>
+          <t>86352</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>127797</t>
+          <t>128623</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>158059</t>
+          <t>158100</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>136646</t>
+          <t>135766</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>157541</t>
+          <t>158238</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>274809</t>
+          <t>273564</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>313051</t>
+          <t>310367</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
